--- a/5/search/FY4_Missile2_results/solutions_direction_324.0.xlsx
+++ b/5/search/FY4_Missile2_results/solutions_direction_324.0.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,34 +487,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>288</v>
+        <v>207</v>
       </c>
       <c r="B2" t="n">
-        <v>123.2</v>
+        <v>102</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>11152.28357482797</v>
+        <v>8818.816028786876</v>
       </c>
       <c r="F2" t="n">
-        <v>1531.319348769748</v>
+        <v>888.6312566375898</v>
       </c>
       <c r="G2" t="n">
         <v>1800</v>
       </c>
       <c r="H2" t="n">
-        <v>11532.99251189791</v>
+        <v>7546.458712245887</v>
       </c>
       <c r="I2" t="n">
-        <v>359.617720694119</v>
+        <v>240.3328230095171</v>
       </c>
       <c r="J2" t="n">
-        <v>1310</v>
+        <v>839.5999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -522,37 +522,597 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>207</v>
+      </c>
+      <c r="B3" t="n">
+        <v>112</v>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9004.145385818056</v>
+      </c>
+      <c r="F3" t="n">
+        <v>983.0612805834154</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7607.047155890695</v>
+      </c>
+      <c r="I3" t="n">
+        <v>271.2041769918062</v>
+      </c>
+      <c r="J3" t="n">
+        <v>839.5999999999999</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>207</v>
+      </c>
+      <c r="B4" t="n">
+        <v>114</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8968.505124850521</v>
+      </c>
+      <c r="F4" t="n">
+        <v>964.9016605938336</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7546.458712245885</v>
+      </c>
+      <c r="I4" t="n">
+        <v>240.3328230095171</v>
+      </c>
+      <c r="J4" t="n">
+        <v>839.5999999999999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>216</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9705.572809000085</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1059.543596332043</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8653.850716312652</v>
+      </c>
+      <c r="I5" t="n">
+        <v>295.4227683518284</v>
+      </c>
+      <c r="J5" t="n">
+        <v>971.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>216</v>
+      </c>
+      <c r="B6" t="n">
+        <v>114</v>
+      </c>
+      <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9893.264751695071</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1195.909774863897</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8694.301566031398</v>
+      </c>
+      <c r="I6" t="n">
+        <v>324.8120309664519</v>
+      </c>
+      <c r="J6" t="n">
+        <v>971.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>216</v>
+      </c>
+      <c r="B7" t="n">
+        <v>116</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>13</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9873.848343830074</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1181.802928808878</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8653.850716312652</v>
+      </c>
+      <c r="I7" t="n">
+        <v>295.4227683518284</v>
+      </c>
+      <c r="J7" t="n">
+        <v>971.9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>216</v>
+      </c>
+      <c r="B8" t="n">
+        <v>136</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10119.78951012006</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1360.489645505789</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8689.44746406515</v>
+      </c>
+      <c r="I8" t="n">
+        <v>321.285319452697</v>
+      </c>
+      <c r="J8" t="n">
+        <v>971.9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>229.5</v>
+      </c>
+      <c r="B9" t="n">
+        <v>138</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10641.50467732174</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1580.255906988783</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9566.018709286955</v>
+      </c>
+      <c r="I9" t="n">
+        <v>321.0236279551311</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1094.4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>234</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102</v>
+      </c>
+      <c r="C10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10520.36723412934</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1339.842132590043</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9800.918085323356</v>
+      </c>
+      <c r="I10" t="n">
+        <v>349.6053314751075</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1094.4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>234</v>
+      </c>
+      <c r="B11" t="n">
+        <v>126</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10703.75623284459</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1592.255434835027</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9815.024931378373</v>
+      </c>
+      <c r="I11" t="n">
+        <v>369.0217393401063</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1094.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>256.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>114</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10893.54891408171</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1556.599316298659</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10600.8084278064</v>
+      </c>
+      <c r="I12" t="n">
+        <v>337.2474361199729</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1207.1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>261</v>
+      </c>
+      <c r="B13" t="n">
+        <v>110</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10931.1688353823</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1565.417130138139</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10741.88313268362</v>
+      </c>
+      <c r="I13" t="n">
+        <v>370.3142380180227</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1207.1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>265.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>108</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10966.10567064557</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1569.331711827289</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H14" t="n">
+        <v>10872.89626492089</v>
+      </c>
+      <c r="I14" t="n">
+        <v>384.9939193523326</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1207.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>288</v>
+      </c>
+      <c r="B15" t="n">
+        <v>122</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="n">
+        <v>11150.80029325497</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1535.884420047965</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H15" t="n">
+        <v>11527.80102639241</v>
+      </c>
+      <c r="I15" t="n">
+        <v>375.5954701678777</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>124</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11189.81098245308</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1541.755751874402</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H16" t="n">
+        <v>11664.3384385858</v>
+      </c>
+      <c r="I16" t="n">
+        <v>396.1451315604063</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>297</v>
       </c>
-      <c r="B3" t="n">
-        <v>100.8</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" t="n">
         <v>8</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D17" t="n">
         <v>10</v>
       </c>
-      <c r="E3" t="n">
-        <v>11366.09793898997</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1281.4923388945</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1800</v>
-      </c>
-      <c r="H3" t="n">
-        <v>11823.72036272743</v>
-      </c>
-      <c r="I3" t="n">
-        <v>383.3577625126252</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="E17" t="n">
+        <v>11363.19239979164</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1287.194780649306</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H17" t="n">
+        <v>11817.18289953118</v>
+      </c>
+      <c r="I17" t="n">
+        <v>396.1882564609375</v>
+      </c>
+      <c r="J17" t="n">
         <v>1310</v>
       </c>
-      <c r="K3" t="n">
-        <v>2</v>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>297</v>
+      </c>
+      <c r="B18" t="n">
+        <v>128</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="n">
+        <v>11232.44313586665</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1543.804659615555</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H18" t="n">
+        <v>11813.55097553327</v>
+      </c>
+      <c r="I18" t="n">
+        <v>403.3163086544444</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>315</v>
+      </c>
+      <c r="B19" t="n">
+        <v>132</v>
+      </c>
+      <c r="C19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>11746.70476093299</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1253.295239067006</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12586.74761698261</v>
+      </c>
+      <c r="I19" t="n">
+        <v>413.252383017387</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1403.1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
